--- a/VerveStacks_IND_grids_kan10/SuppXLS/Scen_TSParameters_ts_24.xlsx
+++ b/VerveStacks_IND_grids_kan10/SuppXLS/Scen_TSParameters_ts_24.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B1E9229F-DD6F-4F9E-BE68-5F58DF8DB7C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B60EA13-290D-4670-80E3-53523F67813D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ev_charging_uc" sheetId="6" r:id="rId1"/>
@@ -1332,13 +1332,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S02aH03,S04aH02,S03aH04,S03aH02,S03aH05,S01aH02,S04aH04,S01aH04,S01aH05,S01aH03,S02aH02,S03aH03,S04aH03,S02aH04,S02aH05,S04aH05</t>
+    <t>S02aH04,S02aH05,S02aH03,S04aH03,S01aH04,S01aH03,S02aH02,S01aH05,S03aH03,S03aH02,S04aH05,S03aH04,S03aH05,S04aH02,S01aH02,S04aH04</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S01aH01,S04aH01,S04aH06,S01aH06,S03aH06,S03aH01,S02aH01,S02aH06</t>
+    <t>S02aH06,S01aH01,S04aH01,S04aH06,S02aH01,S01aH06,S03aH01,S03aH06</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1933,7 +1933,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S01aH01,S04aH01,S04aH06,S01aH06,S03aH06,S03aH01,S02aH01,S02aH06</v>
+        <v>S02aH06,S01aH01,S04aH01,S04aH06,S02aH01,S01aH06,S03aH01,S03aH06</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S02aH03,S04aH02,S03aH04,S03aH02,S03aH05,S01aH02,S04aH04,S01aH04,S01aH05,S01aH03,S02aH02,S03aH03,S04aH03,S02aH04,S02aH05,S04aH05</v>
+        <v>S02aH04,S02aH05,S02aH03,S04aH03,S01aH04,S01aH03,S02aH02,S01aH05,S03aH03,S03aH02,S04aH05,S03aH04,S03aH05,S04aH02,S01aH02,S04aH04</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -2061,7 +2061,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEA5E777-478A-46B0-97A5-98193F55474D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D4A40BF-B3E3-4870-8669-A49DAB58C6BE}">
   <dimension ref="A9:G16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2167,7 +2167,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CF7B2C2-76C2-4AD0-8D43-C71882635A53}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D7192FD-074B-4219-A874-11B2308D6C42}">
   <dimension ref="B9:O1882"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -54645,7 +54645,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11BF355F-ECA5-4770-91B5-43DA80E375AA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC273C8D-AC4F-4003-95F5-41E44F552C7D}">
   <dimension ref="B9:DH179"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -83691,7 +83691,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75AB5B4D-8B78-4684-9D25-F6229C0693F9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{427CF1B0-58E4-4E59-818E-AD65CDFC8C03}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -83799,7 +83799,7 @@
         <v>37</v>
       </c>
       <c r="R11">
-        <v>0.26990853121428832</v>
+        <v>0.26990853121428826</v>
       </c>
       <c r="S11" t="s">
         <v>439</v>
@@ -84250,7 +84250,7 @@
         <v>45</v>
       </c>
       <c r="R22">
-        <v>0.5036131997609502</v>
+        <v>0.50361319976095009</v>
       </c>
       <c r="S22" t="s">
         <v>439</v>
@@ -84414,7 +84414,7 @@
         <v>45</v>
       </c>
       <c r="R26">
-        <v>0.55593333333333328</v>
+        <v>0.55593333333333339</v>
       </c>
       <c r="S26" t="s">
         <v>439</v>
@@ -84762,7 +84762,7 @@
         <v>37</v>
       </c>
       <c r="R35">
-        <v>0.24966666666666668</v>
+        <v>0.2496666666666667</v>
       </c>
       <c r="S35" t="s">
         <v>439</v>
@@ -85142,7 +85142,7 @@
         <v>45</v>
       </c>
       <c r="R54">
-        <v>0.42126666666666668</v>
+        <v>0.42126666666666662</v>
       </c>
       <c r="S54" t="s">
         <v>439</v>
@@ -85222,7 +85222,7 @@
         <v>45</v>
       </c>
       <c r="R58">
-        <v>0.44933333333333336</v>
+        <v>0.44933333333333331</v>
       </c>
       <c r="S58" t="s">
         <v>439</v>
@@ -85278,7 +85278,7 @@
         <v>45</v>
       </c>
       <c r="R62">
-        <v>0.43849999999999995</v>
+        <v>0.43850000000000006</v>
       </c>
       <c r="S62" t="s">
         <v>439</v>
@@ -85292,7 +85292,7 @@
         <v>37</v>
       </c>
       <c r="R63">
-        <v>0.25706666666666672</v>
+        <v>0.25706666666666667</v>
       </c>
       <c r="S63" t="s">
         <v>439</v>
@@ -85334,7 +85334,7 @@
         <v>45</v>
       </c>
       <c r="R66">
-        <v>0.435</v>
+        <v>0.43500000000000005</v>
       </c>
       <c r="S66" t="s">
         <v>439</v>
@@ -85390,7 +85390,7 @@
         <v>45</v>
       </c>
       <c r="R70">
-        <v>0.43786666666666668</v>
+        <v>0.43786666666666663</v>
       </c>
       <c r="S70" t="s">
         <v>439</v>
@@ -85782,7 +85782,7 @@
         <v>45</v>
       </c>
       <c r="R98">
-        <v>0.39066666666666672</v>
+        <v>0.39066666666666666</v>
       </c>
       <c r="S98" t="s">
         <v>439</v>
@@ -86020,7 +86020,7 @@
         <v>37</v>
       </c>
       <c r="R115">
-        <v>0.24033333333333332</v>
+        <v>0.24033333333333337</v>
       </c>
       <c r="S115" t="s">
         <v>439</v>
@@ -86062,7 +86062,7 @@
         <v>45</v>
       </c>
       <c r="R118">
-        <v>0.44803333333333334</v>
+        <v>0.44803333333333328</v>
       </c>
       <c r="S118" t="s">
         <v>439</v>

--- a/VerveStacks_IND_grids_kan10/SuppXLS/Scen_TSParameters_ts_24.xlsx
+++ b/VerveStacks_IND_grids_kan10/SuppXLS/Scen_TSParameters_ts_24.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B60EA13-290D-4670-80E3-53523F67813D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73C3A9FE-C2B6-4D3D-986B-66551190C4B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ev_charging_uc" sheetId="6" r:id="rId1"/>
@@ -19,9 +19,6 @@
     <sheet name="firmness" sheetId="9" r:id="rId4"/>
     <sheet name="load_demand_peak_hydro" sheetId="10" r:id="rId5"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId6"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -40,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13822" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13823" uniqueCount="440">
   <si>
     <t>share of charging at night</t>
   </si>
@@ -1332,13 +1329,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S02aH04,S02aH05,S02aH03,S04aH03,S01aH04,S01aH03,S02aH02,S01aH05,S03aH03,S03aH02,S04aH05,S03aH04,S03aH05,S04aH02,S01aH02,S04aH04</t>
+    <t>S03aH02,S03aH05,S03aH04,S03aH03,S01aH04,S02aH04,S02aH05,S04aH05,S04aH02,S04aH03,S01aH05,S01aH03,S01aH02,S04aH04,S02aH02,S02aH03</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S02aH06,S01aH01,S04aH01,S04aH06,S02aH01,S01aH06,S03aH01,S03aH06</t>
+    <t>S01aH06,S02aH06,S02aH01,S03aH06,S03aH01,S01aH01,S04aH01,S04aH06</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1499,19 +1496,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Veda"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1835,9 +1819,8 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="str">
-        <f>IFERROR([1]Veda!D5,"ts_24")</f>
-        <v>ts_24</v>
+      <c r="A10" t="s">
+        <v>49</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5" t="s">
@@ -1933,7 +1916,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S02aH06,S01aH01,S04aH01,S04aH06,S02aH01,S01aH06,S03aH01,S03aH06</v>
+        <v>S01aH06,S02aH06,S02aH01,S03aH06,S03aH01,S01aH01,S04aH01,S04aH06</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1965,7 +1948,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S02aH04,S02aH05,S02aH03,S04aH03,S01aH04,S01aH03,S02aH02,S01aH05,S03aH03,S03aH02,S04aH05,S03aH04,S03aH05,S04aH02,S01aH02,S04aH04</v>
+        <v>S03aH02,S03aH05,S03aH04,S03aH03,S01aH04,S02aH04,S02aH05,S04aH05,S04aH02,S04aH03,S01aH05,S01aH03,S01aH02,S04aH04,S02aH02,S02aH03</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -2061,7 +2044,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D4A40BF-B3E3-4870-8669-A49DAB58C6BE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4261D7A-8A87-42A2-9D9F-6EE5D1A63616}">
   <dimension ref="A9:G16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2092,10 +2075,6 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="str">
-        <f>IFERROR(IF([1]Veda!D5=A10,"ok","x"),"")</f>
-        <v/>
-      </c>
       <c r="C11" t="s">
         <v>37</v>
       </c>
@@ -2167,7 +2146,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D7192FD-074B-4219-A874-11B2308D6C42}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37902148-D177-4D80-8E80-7669895756C7}">
   <dimension ref="B9:O1882"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -54645,7 +54624,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC273C8D-AC4F-4003-95F5-41E44F552C7D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EEB68A0-EE24-46BB-A5F9-F322E486727F}">
   <dimension ref="B9:DH179"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -83691,7 +83670,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{427CF1B0-58E4-4E59-818E-AD65CDFC8C03}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AF26BE1-D94B-4670-B894-AC1B6D59341A}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -83761,10 +83740,6 @@
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A11" t="str">
-        <f>IFERROR(IF([1]Veda!D5=A10,"ok","x"),"")</f>
-        <v/>
-      </c>
       <c r="C11">
         <v>8.2191780821917804E-2</v>
       </c>
@@ -83881,7 +83856,7 @@
         <v>43</v>
       </c>
       <c r="R13">
-        <v>0.56168582465078842</v>
+        <v>0.56168582465078831</v>
       </c>
       <c r="S13" t="s">
         <v>439</v>
@@ -84045,7 +84020,7 @@
         <v>43</v>
       </c>
       <c r="R17">
-        <v>0.56513738013620785</v>
+        <v>0.56513738013620773</v>
       </c>
       <c r="S17" t="s">
         <v>439</v>
@@ -84250,7 +84225,7 @@
         <v>45</v>
       </c>
       <c r="R22">
-        <v>0.50361319976095009</v>
+        <v>0.5036131997609502</v>
       </c>
       <c r="S22" t="s">
         <v>439</v>
@@ -84414,7 +84389,7 @@
         <v>45</v>
       </c>
       <c r="R26">
-        <v>0.55593333333333339</v>
+        <v>0.55593333333333328</v>
       </c>
       <c r="S26" t="s">
         <v>439</v>
@@ -84537,7 +84512,7 @@
         <v>43</v>
       </c>
       <c r="R29">
-        <v>0.61353333333333326</v>
+        <v>0.61353333333333337</v>
       </c>
       <c r="S29" t="s">
         <v>439</v>
@@ -84802,7 +84777,7 @@
         <v>43</v>
       </c>
       <c r="R37">
-        <v>0.56366666666666676</v>
+        <v>0.56366666666666665</v>
       </c>
       <c r="S37" t="s">
         <v>439</v>
@@ -84962,7 +84937,7 @@
         <v>43</v>
       </c>
       <c r="R45">
-        <v>0.55986666666666662</v>
+        <v>0.55986666666666673</v>
       </c>
       <c r="S45" t="s">
         <v>439</v>
@@ -85142,7 +85117,7 @@
         <v>45</v>
       </c>
       <c r="R54">
-        <v>0.42126666666666662</v>
+        <v>0.42126666666666668</v>
       </c>
       <c r="S54" t="s">
         <v>439</v>
@@ -85222,7 +85197,7 @@
         <v>45</v>
       </c>
       <c r="R58">
-        <v>0.44933333333333331</v>
+        <v>0.44933333333333336</v>
       </c>
       <c r="S58" t="s">
         <v>439</v>
@@ -85278,7 +85253,7 @@
         <v>45</v>
       </c>
       <c r="R62">
-        <v>0.43850000000000006</v>
+        <v>0.43849999999999995</v>
       </c>
       <c r="S62" t="s">
         <v>439</v>
@@ -85320,7 +85295,7 @@
         <v>43</v>
       </c>
       <c r="R65">
-        <v>0.54843333333333322</v>
+        <v>0.54843333333333333</v>
       </c>
       <c r="S65" t="s">
         <v>439</v>
@@ -85334,7 +85309,7 @@
         <v>45</v>
       </c>
       <c r="R66">
-        <v>0.43500000000000005</v>
+        <v>0.435</v>
       </c>
       <c r="S66" t="s">
         <v>439</v>
@@ -85376,7 +85351,7 @@
         <v>43</v>
       </c>
       <c r="R69">
-        <v>0.55679999999999996</v>
+        <v>0.55680000000000007</v>
       </c>
       <c r="S69" t="s">
         <v>439</v>
@@ -85390,7 +85365,7 @@
         <v>45</v>
       </c>
       <c r="R70">
-        <v>0.43786666666666663</v>
+        <v>0.43786666666666668</v>
       </c>
       <c r="S70" t="s">
         <v>439</v>
@@ -85432,7 +85407,7 @@
         <v>43</v>
       </c>
       <c r="R73">
-        <v>0.54473333333333329</v>
+        <v>0.5447333333333334</v>
       </c>
       <c r="S73" t="s">
         <v>439</v>
@@ -85600,7 +85575,7 @@
         <v>43</v>
       </c>
       <c r="R85">
-        <v>0.55886666666666673</v>
+        <v>0.55886666666666662</v>
       </c>
       <c r="S85" t="s">
         <v>439</v>
@@ -85656,7 +85631,7 @@
         <v>43</v>
       </c>
       <c r="R89">
-        <v>0.46700000000000003</v>
+        <v>0.46699999999999992</v>
       </c>
       <c r="S89" t="s">
         <v>439</v>
@@ -85768,7 +85743,7 @@
         <v>43</v>
       </c>
       <c r="R97">
-        <v>0.47156666666666669</v>
+        <v>0.47156666666666663</v>
       </c>
       <c r="S97" t="s">
         <v>439</v>
@@ -85782,7 +85757,7 @@
         <v>45</v>
       </c>
       <c r="R98">
-        <v>0.39066666666666666</v>
+        <v>0.39066666666666672</v>
       </c>
       <c r="S98" t="s">
         <v>439</v>
@@ -85992,7 +85967,7 @@
         <v>43</v>
       </c>
       <c r="R113">
-        <v>0.54623333333333335</v>
+        <v>0.54623333333333324</v>
       </c>
       <c r="S113" t="s">
         <v>439</v>
@@ -86062,7 +86037,7 @@
         <v>45</v>
       </c>
       <c r="R118">
-        <v>0.44803333333333328</v>
+        <v>0.44803333333333334</v>
       </c>
       <c r="S118" t="s">
         <v>439</v>

--- a/VerveStacks_IND_grids_kan10/SuppXLS/Scen_TSParameters_ts_24.xlsx
+++ b/VerveStacks_IND_grids_kan10/SuppXLS/Scen_TSParameters_ts_24.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73C3A9FE-C2B6-4D3D-986B-66551190C4B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9E7B511-18D6-481D-95F0-283BD0746647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1329,13 +1329,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S03aH02,S03aH05,S03aH04,S03aH03,S01aH04,S02aH04,S02aH05,S04aH05,S04aH02,S04aH03,S01aH05,S01aH03,S01aH02,S04aH04,S02aH02,S02aH03</t>
+    <t>S01aH03,S04aH05,S02aH04,S02aH05,S04aH03,S02aH03,S04aH02,S03aH05,S02aH02,S01aH04,S03aH04,S03aH02,S01aH05,S03aH03,S01aH02,S04aH04</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S01aH06,S02aH06,S02aH01,S03aH06,S03aH01,S01aH01,S04aH01,S04aH06</t>
+    <t>S02aH06,S02aH01,S01aH01,S04aH01,S04aH06,S03aH01,S01aH06,S03aH06</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S01aH06,S02aH06,S02aH01,S03aH06,S03aH01,S01aH01,S04aH01,S04aH06</v>
+        <v>S02aH06,S02aH01,S01aH01,S04aH01,S04aH06,S03aH01,S01aH06,S03aH06</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S03aH02,S03aH05,S03aH04,S03aH03,S01aH04,S02aH04,S02aH05,S04aH05,S04aH02,S04aH03,S01aH05,S01aH03,S01aH02,S04aH04,S02aH02,S02aH03</v>
+        <v>S01aH03,S04aH05,S02aH04,S02aH05,S04aH03,S02aH03,S04aH02,S03aH05,S02aH02,S01aH04,S03aH04,S03aH02,S01aH05,S03aH03,S01aH02,S04aH04</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -2044,7 +2044,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4261D7A-8A87-42A2-9D9F-6EE5D1A63616}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3358CA96-57B4-4403-8A9D-FA6402B56AEE}">
   <dimension ref="A9:G16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2146,7 +2146,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37902148-D177-4D80-8E80-7669895756C7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2648BE13-EC25-4A37-AE6F-BDBCD0365244}">
   <dimension ref="B9:O1882"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -54624,7 +54624,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EEB68A0-EE24-46BB-A5F9-F322E486727F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31684B10-2D8D-4B83-BE87-7EECEA57A306}">
   <dimension ref="B9:DH179"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -83670,7 +83670,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AF26BE1-D94B-4670-B894-AC1B6D59341A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA06196A-28C3-45A8-9B70-5ED9BDF56C02}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -83774,7 +83774,7 @@
         <v>37</v>
       </c>
       <c r="R11">
-        <v>0.26990853121428826</v>
+        <v>0.26990853121428821</v>
       </c>
       <c r="S11" t="s">
         <v>439</v>
@@ -83856,7 +83856,7 @@
         <v>43</v>
       </c>
       <c r="R13">
-        <v>0.56168582465078831</v>
+        <v>0.56168582465078842</v>
       </c>
       <c r="S13" t="s">
         <v>439</v>
@@ -83938,7 +83938,7 @@
         <v>37</v>
       </c>
       <c r="R15">
-        <v>0.25029049486358229</v>
+        <v>0.25029049486358235</v>
       </c>
       <c r="S15" t="s">
         <v>439</v>
@@ -84020,7 +84020,7 @@
         <v>43</v>
       </c>
       <c r="R17">
-        <v>0.56513738013620773</v>
+        <v>0.56513738013620785</v>
       </c>
       <c r="S17" t="s">
         <v>439</v>
@@ -84102,7 +84102,7 @@
         <v>37</v>
       </c>
       <c r="R19">
-        <v>0.24894096398789592</v>
+        <v>0.24894096398789589</v>
       </c>
       <c r="S19" t="s">
         <v>439</v>
@@ -84225,7 +84225,7 @@
         <v>45</v>
       </c>
       <c r="R22">
-        <v>0.5036131997609502</v>
+        <v>0.50361319976095009</v>
       </c>
       <c r="S22" t="s">
         <v>439</v>
@@ -84389,7 +84389,7 @@
         <v>45</v>
       </c>
       <c r="R26">
-        <v>0.55593333333333328</v>
+        <v>0.55593333333333339</v>
       </c>
       <c r="S26" t="s">
         <v>439</v>
@@ -84512,7 +84512,7 @@
         <v>43</v>
       </c>
       <c r="R29">
-        <v>0.61353333333333337</v>
+        <v>0.61353333333333326</v>
       </c>
       <c r="S29" t="s">
         <v>439</v>
@@ -84737,7 +84737,7 @@
         <v>37</v>
       </c>
       <c r="R35">
-        <v>0.2496666666666667</v>
+        <v>0.24966666666666668</v>
       </c>
       <c r="S35" t="s">
         <v>439</v>
@@ -84757,7 +84757,7 @@
         <v>41</v>
       </c>
       <c r="R36">
-        <v>0.32713333333333333</v>
+        <v>0.32713333333333328</v>
       </c>
       <c r="S36" t="s">
         <v>439</v>
@@ -84777,7 +84777,7 @@
         <v>43</v>
       </c>
       <c r="R37">
-        <v>0.56366666666666665</v>
+        <v>0.56366666666666676</v>
       </c>
       <c r="S37" t="s">
         <v>439</v>
@@ -84937,7 +84937,7 @@
         <v>43</v>
       </c>
       <c r="R45">
-        <v>0.55986666666666673</v>
+        <v>0.55986666666666662</v>
       </c>
       <c r="S45" t="s">
         <v>439</v>
@@ -84977,7 +84977,7 @@
         <v>37</v>
       </c>
       <c r="R47">
-        <v>0.25330000000000003</v>
+        <v>0.25329999999999997</v>
       </c>
       <c r="S47" t="s">
         <v>439</v>
@@ -85077,7 +85077,7 @@
         <v>41</v>
       </c>
       <c r="R52">
-        <v>0.32830000000000004</v>
+        <v>0.32829999999999998</v>
       </c>
       <c r="S52" t="s">
         <v>439</v>
@@ -85117,7 +85117,7 @@
         <v>45</v>
       </c>
       <c r="R54">
-        <v>0.42126666666666668</v>
+        <v>0.42126666666666662</v>
       </c>
       <c r="S54" t="s">
         <v>439</v>
@@ -85197,7 +85197,7 @@
         <v>45</v>
       </c>
       <c r="R58">
-        <v>0.44933333333333336</v>
+        <v>0.44933333333333331</v>
       </c>
       <c r="S58" t="s">
         <v>439</v>
@@ -85253,7 +85253,7 @@
         <v>45</v>
       </c>
       <c r="R62">
-        <v>0.43849999999999995</v>
+        <v>0.43850000000000006</v>
       </c>
       <c r="S62" t="s">
         <v>439</v>
@@ -85267,7 +85267,7 @@
         <v>37</v>
       </c>
       <c r="R63">
-        <v>0.25706666666666667</v>
+        <v>0.25706666666666672</v>
       </c>
       <c r="S63" t="s">
         <v>439</v>
@@ -85295,7 +85295,7 @@
         <v>43</v>
       </c>
       <c r="R65">
-        <v>0.54843333333333333</v>
+        <v>0.54843333333333322</v>
       </c>
       <c r="S65" t="s">
         <v>439</v>
@@ -85309,7 +85309,7 @@
         <v>45</v>
       </c>
       <c r="R66">
-        <v>0.435</v>
+        <v>0.43500000000000005</v>
       </c>
       <c r="S66" t="s">
         <v>439</v>
@@ -85351,7 +85351,7 @@
         <v>43</v>
       </c>
       <c r="R69">
-        <v>0.55680000000000007</v>
+        <v>0.55679999999999996</v>
       </c>
       <c r="S69" t="s">
         <v>439</v>
@@ -85365,7 +85365,7 @@
         <v>45</v>
       </c>
       <c r="R70">
-        <v>0.43786666666666668</v>
+        <v>0.43786666666666663</v>
       </c>
       <c r="S70" t="s">
         <v>439</v>
@@ -85379,7 +85379,7 @@
         <v>37</v>
       </c>
       <c r="R71">
-        <v>0.25716666666666671</v>
+        <v>0.25716666666666665</v>
       </c>
       <c r="S71" t="s">
         <v>439</v>
@@ -85407,7 +85407,7 @@
         <v>43</v>
       </c>
       <c r="R73">
-        <v>0.5447333333333334</v>
+        <v>0.54473333333333329</v>
       </c>
       <c r="S73" t="s">
         <v>439</v>
@@ -85505,7 +85505,7 @@
         <v>41</v>
       </c>
       <c r="R80">
-        <v>0.32556666666666673</v>
+        <v>0.32556666666666667</v>
       </c>
       <c r="S80" t="s">
         <v>439</v>
@@ -85547,7 +85547,7 @@
         <v>37</v>
       </c>
       <c r="R83">
-        <v>0.25283333333333335</v>
+        <v>0.2528333333333333</v>
       </c>
       <c r="S83" t="s">
         <v>439</v>
@@ -85575,7 +85575,7 @@
         <v>43</v>
       </c>
       <c r="R85">
-        <v>0.55886666666666662</v>
+        <v>0.55886666666666673</v>
       </c>
       <c r="S85" t="s">
         <v>439</v>
@@ -85617,7 +85617,7 @@
         <v>41</v>
       </c>
       <c r="R88">
-        <v>0.2752</v>
+        <v>0.27519999999999994</v>
       </c>
       <c r="S88" t="s">
         <v>439</v>
@@ -85631,7 +85631,7 @@
         <v>43</v>
       </c>
       <c r="R89">
-        <v>0.46699999999999992</v>
+        <v>0.46700000000000003</v>
       </c>
       <c r="S89" t="s">
         <v>439</v>
@@ -85743,7 +85743,7 @@
         <v>43</v>
       </c>
       <c r="R97">
-        <v>0.47156666666666663</v>
+        <v>0.47156666666666669</v>
       </c>
       <c r="S97" t="s">
         <v>439</v>
@@ -85757,7 +85757,7 @@
         <v>45</v>
       </c>
       <c r="R98">
-        <v>0.39066666666666672</v>
+        <v>0.39066666666666666</v>
       </c>
       <c r="S98" t="s">
         <v>439</v>
@@ -85883,7 +85883,7 @@
         <v>37</v>
       </c>
       <c r="R107">
-        <v>0.29300000000000004</v>
+        <v>0.29299999999999998</v>
       </c>
       <c r="S107" t="s">
         <v>439</v>
@@ -85967,7 +85967,7 @@
         <v>43</v>
       </c>
       <c r="R113">
-        <v>0.54623333333333324</v>
+        <v>0.54623333333333335</v>
       </c>
       <c r="S113" t="s">
         <v>439</v>
@@ -85995,7 +85995,7 @@
         <v>37</v>
       </c>
       <c r="R115">
-        <v>0.24033333333333337</v>
+        <v>0.24033333333333332</v>
       </c>
       <c r="S115" t="s">
         <v>439</v>
@@ -86009,7 +86009,7 @@
         <v>41</v>
       </c>
       <c r="R116">
-        <v>0.33780000000000004</v>
+        <v>0.33779999999999993</v>
       </c>
       <c r="S116" t="s">
         <v>439</v>
@@ -86037,7 +86037,7 @@
         <v>45</v>
       </c>
       <c r="R118">
-        <v>0.44803333333333334</v>
+        <v>0.44803333333333328</v>
       </c>
       <c r="S118" t="s">
         <v>439</v>
